--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="Q2" t="n">
         <v>173</v>
       </c>
       <c r="R2" t="n">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3566</v>
+        <v>3586</v>
       </c>
       <c r="Q3" t="n">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="R3" t="n">
-        <v>4128</v>
+        <v>4156</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>퍼시스트피트니스 보라점</t>
+          <t>스타트짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>doublekgym05@naver.com</t>
+          <t>startgym9@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-282-9688</t>
+          <t>0507-1411-8593</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 한보라1로10번길 6-10 휘성빌딩 3층 퍼시스트피트니스</t>
+          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doublekgym05/223662020470</t>
+          <t>https://www.instagram.com/start_gym_no.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1694</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1884</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>3578</v>
+        <v>113</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36952740</t>
+          <t>1252102661</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36952740</t>
+          <t>https://m.place.naver.com/place/1252102661</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
+          <t>비전휘트니스 수지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy46@naver.com</t>
+          <t>visionfitness777@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1398-7945</t>
+          <t>0507-1368-4687</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
+          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy46</t>
+          <t>https://litt.ly/vision7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1015</v>
+        <v>837</v>
       </c>
       <c r="Q5" t="n">
-        <v>615</v>
+        <v>1361</v>
       </c>
       <c r="R5" t="n">
-        <v>1630</v>
+        <v>2198</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1979518055</t>
+          <t>1883516104</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979518055</t>
+          <t>https://m.place.naver.com/place/1883516104</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>광교PT필라테스 여성전용 업텐션핏 광교상현본점</t>
+          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bodycoach11@naver.com</t>
+          <t>healthboy46@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1369-7497</t>
+          <t>0507-1398-7945</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교중앙로 308 9층 901호</t>
+          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://linktr.ee/uptensionfit</t>
+          <t>https://blog.naver.com/healthboy46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>549</v>
+        <v>1017</v>
       </c>
       <c r="Q6" t="n">
-        <v>1070</v>
+        <v>619</v>
       </c>
       <c r="R6" t="n">
-        <v>1619</v>
+        <v>1636</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1493352843</t>
+          <t>1979518055</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493352843</t>
+          <t>https://m.place.naver.com/place/1979518055</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>운동에반하다 기흥점</t>
+          <t>보스턴짐 상갈점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kmy0140@naver.com</t>
+          <t>bostongym44@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1372-9642</t>
+          <t>0507-1312-1996</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 구갈로 64 7층 703호</t>
+          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kmy0140</t>
+          <t>https://www.instagram.com/bostongym_4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>182</v>
+        <v>1346</v>
       </c>
       <c r="Q7" t="n">
-        <v>947</v>
+        <v>756</v>
       </c>
       <c r="R7" t="n">
-        <v>1129</v>
+        <v>2102</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1474657534</t>
+          <t>1333671976</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1474657534</t>
+          <t>https://m.place.naver.com/place/1333671976</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비전휘트니스 수지점</t>
+          <t>헬스보이짐PT 상현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>visionfitness777@naver.com</t>
+          <t>healthboy64@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1368-4687</t>
+          <t>0507-1383-8929</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
+          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://litt.ly/vision7</t>
+          <t>https://www.instagram.com/healthboy64/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>827</v>
+        <v>941</v>
       </c>
       <c r="Q8" t="n">
-        <v>1339</v>
+        <v>715</v>
       </c>
       <c r="R8" t="n">
-        <v>2166</v>
+        <v>1656</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1883516104</t>
+          <t>1266933778</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883516104</t>
+          <t>https://m.place.naver.com/place/1266933778</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐PT 상현점</t>
+          <t>뷰티풀몬스터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboy64@naver.com</t>
+          <t>stryper1983@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1383-8929</t>
+          <t>0507-1412-1006</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
+          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy64/</t>
+          <t>https://blog.naver.com/stryper1983</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>935</v>
+        <v>1348</v>
       </c>
       <c r="Q9" t="n">
-        <v>707</v>
+        <v>325</v>
       </c>
       <c r="R9" t="n">
-        <v>1642</v>
+        <v>1673</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1266933778</t>
+          <t>37489444</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266933778</t>
+          <t>https://m.place.naver.com/place/37489444</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>청담피트니스</t>
+          <t>넥스트짐 용인 강남대점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cdam2888@naver.com</t>
+          <t>nextgym04@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1361-2889</t>
+          <t>0507-1327-9679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 명지로60번길 8-12 4층</t>
+          <t>경기도 용인시 기흥구 강남로 3 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cdam2888</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1741</v>
+        <v>620</v>
       </c>
       <c r="Q10" t="n">
-        <v>431</v>
+        <v>115</v>
       </c>
       <c r="R10" t="n">
-        <v>2172</v>
+        <v>735</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1073785917</t>
+          <t>2078374448</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073785917</t>
+          <t>https://m.place.naver.com/place/2078374448</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리플랜운동센터 재활.체형교정.PT</t>
+          <t>청담피트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kyweee213@naver.com</t>
+          <t>cdam2888@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1304-3762</t>
+          <t>0507-1361-2889</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
+          <t>경기도 용인시 처인구 명지로60번길 8-12 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kyweee213</t>
+          <t>https://blog.naver.com/cdam2888</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,36 +1463,130 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
+        <v>1751</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>434</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2185</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1073785917</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1073785917</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>척추,자세교정</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>리플랜운동센터 재활.체형교정.PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>kyweee213@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1304-3762</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kyweee213</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>83</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>147</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>230</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1269639617</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1269639617</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Q2" t="n">
         <v>173</v>
       </c>
       <c r="R2" t="n">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>런던피트니스 &amp; 헬스 &amp; PT 보정점</t>
+          <t>스타트짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>startgym9@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1429-9680</t>
+          <t>0507-1411-8593</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 죽전로 20 죽전누리에뜰 B동 B1층</t>
+          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>https://www.instagram.com/start_gym_no.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3586</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="n">
-        <v>570</v>
+        <v>34</v>
       </c>
       <c r="R3" t="n">
-        <v>4156</v>
+        <v>113</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,56 +730,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1409535054</t>
+          <t>1252102661</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409535054</t>
+          <t>https://m.place.naver.com/place/1252102661</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스타트짐</t>
+          <t>비전휘트니스 수지점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>startgym9@naver.com</t>
+          <t>visionfitness777@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1411-8593</t>
+          <t>0507-1368-4687</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
+          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/start_gym_no.1</t>
+          <t>https://litt.ly/vision7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>79</v>
+        <v>841</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>1363</v>
       </c>
       <c r="R4" t="n">
-        <v>113</v>
+        <v>2204</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1252102661</t>
+          <t>1883516104</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252102661</t>
+          <t>https://m.place.naver.com/place/1883516104</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비전휘트니스 수지점</t>
+          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>visionfitness777@naver.com</t>
+          <t>healthboy46@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-4687</t>
+          <t>0507-1398-7945</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
+          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/vision7</t>
+          <t>https://blog.naver.com/healthboy46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>837</v>
+        <v>1017</v>
       </c>
       <c r="Q5" t="n">
-        <v>1361</v>
+        <v>620</v>
       </c>
       <c r="R5" t="n">
-        <v>2198</v>
+        <v>1637</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1883516104</t>
+          <t>1979518055</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883516104</t>
+          <t>https://m.place.naver.com/place/1979518055</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
+          <t>보스턴짐 상갈점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy46@naver.com</t>
+          <t>bostongym44@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1398-7945</t>
+          <t>0507-1312-1996</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
+          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy46</t>
+          <t>https://www.instagram.com/bostongym_4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1017</v>
+        <v>1349</v>
       </c>
       <c r="Q6" t="n">
-        <v>619</v>
+        <v>756</v>
       </c>
       <c r="R6" t="n">
-        <v>1636</v>
+        <v>2105</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1979518055</t>
+          <t>1333671976</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979518055</t>
+          <t>https://m.place.naver.com/place/1333671976</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>보스턴짐 상갈점 헬스 PT</t>
+          <t>헬스보이짐PT 상현점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bostongym44@naver.com</t>
+          <t>healthboy64@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-1996</t>
+          <t>0507-1383-8929</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
+          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bostongym_4</t>
+          <t>https://www.instagram.com/healthboy64/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1346</v>
+        <v>942</v>
       </c>
       <c r="Q7" t="n">
-        <v>756</v>
+        <v>716</v>
       </c>
       <c r="R7" t="n">
-        <v>2102</v>
+        <v>1658</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1333671976</t>
+          <t>1266933778</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333671976</t>
+          <t>https://m.place.naver.com/place/1266933778</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐PT 상현점</t>
+          <t>뷰티풀몬스터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy64@naver.com</t>
+          <t>stryper1983@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1383-8929</t>
+          <t>0507-1412-1006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
+          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy64/</t>
+          <t>https://blog.naver.com/stryper1983</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>941</v>
+        <v>1348</v>
       </c>
       <c r="Q8" t="n">
-        <v>715</v>
+        <v>326</v>
       </c>
       <c r="R8" t="n">
-        <v>1656</v>
+        <v>1674</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1200,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1266933778</t>
+          <t>37489444</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266933778</t>
+          <t>https://m.place.naver.com/place/37489444</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>뷰티풀몬스터</t>
+          <t>넥스트짐 용인 강남대점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>stryper1983@naver.com</t>
+          <t>nextgym04@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1412-1006</t>
+          <t>0507-1327-9679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
+          <t>경기도 용인시 기흥구 강남로 3 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/stryper1983</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1348</v>
+        <v>621</v>
       </c>
       <c r="Q9" t="n">
-        <v>325</v>
+        <v>116</v>
       </c>
       <c r="R9" t="n">
-        <v>1673</v>
+        <v>737</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37489444</t>
+          <t>2078374448</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37489444</t>
+          <t>https://m.place.naver.com/place/2078374448</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>넥스트짐 용인 강남대점 헬스 PT</t>
+          <t>청담피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nextgym04@naver.com</t>
+          <t>cdam2888@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1327-9679</t>
+          <t>0507-1361-2889</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 강남로 3 7층</t>
+          <t>경기도 용인시 처인구 명지로60번길 8-12 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/cdam2888</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>620</v>
+        <v>1755</v>
       </c>
       <c r="Q10" t="n">
-        <v>115</v>
+        <v>435</v>
       </c>
       <c r="R10" t="n">
-        <v>735</v>
+        <v>2190</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2078374448</t>
+          <t>1073785917</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2078374448</t>
+          <t>https://m.place.naver.com/place/1073785917</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>청담피트니스</t>
+          <t>리플랜운동센터 재활.체형교정.PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cdam2888@naver.com</t>
+          <t>kyweee213@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1361-2889</t>
+          <t>0507-1304-3762</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 명지로60번길 8-12 4층</t>
+          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cdam2888</t>
+          <t>https://blog.naver.com/kyweee213</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1751</v>
+        <v>83</v>
       </c>
       <c r="Q11" t="n">
-        <v>434</v>
+        <v>147</v>
       </c>
       <c r="R11" t="n">
-        <v>2185</v>
+        <v>230</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,56 +1482,56 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1073785917</t>
+          <t>1269639617</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073785917</t>
+          <t>https://m.place.naver.com/place/1269639617</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>리플랜운동센터 재활.체형교정.PT</t>
+          <t>닉필라테스 앤 바디워크</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kyweee213@naver.com</t>
+          <t>nikpilates@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1304-3762</t>
+          <t>0507-1408-9690</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
+          <t>경기 용인시 수지구 신봉1로 165 동광프라자 304~306호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kyweee213</t>
+          <t>http://pf.kakao.com/_xgxgXPn</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1541,33 +1541,37 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vwc6</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="Q12" t="n">
-        <v>147</v>
+        <v>515</v>
       </c>
       <c r="R12" t="n">
-        <v>230</v>
+        <v>637</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1269639617</t>
+          <t>1396914479</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1269639617</t>
+          <t>https://m.place.naver.com/place/1396914479</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>런던피트니스 &amp; 헬스 &amp; PT 보정점</t>
+          <t>스타트짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>startgym9@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1429-9680</t>
+          <t>0507-1411-8593</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 죽전로 20 죽전누리에뜰 B동 B1층</t>
+          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>https://www.instagram.com/start_gym_no.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3587</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="n">
-        <v>570</v>
+        <v>34</v>
       </c>
       <c r="R3" t="n">
-        <v>4157</v>
+        <v>113</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1409535054</t>
+          <t>1252102661</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409535054</t>
+          <t>https://m.place.naver.com/place/1252102661</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,39 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스타트짐</t>
+          <t>비전휘트니스 수지점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>startgym9@naver.com</t>
+          <t>visionfitness777@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1411-8593</t>
+          <t>0507-1368-4687</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
+          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/start_gym_no.1</t>
+          <t>https://litt.ly/vision7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>79</v>
+        <v>841</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>1363</v>
       </c>
       <c r="R4" t="n">
-        <v>113</v>
+        <v>2204</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1252102661</t>
+          <t>1883516104</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252102661</t>
+          <t>https://m.place.naver.com/place/1883516104</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비전휘트니스 수지점</t>
+          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>visionfitness777@naver.com</t>
+          <t>healthboy46@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-4687</t>
+          <t>0507-1398-7945</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
+          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/vision7</t>
+          <t>https://blog.naver.com/healthboy46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>841</v>
+        <v>1017</v>
       </c>
       <c r="Q5" t="n">
-        <v>1363</v>
+        <v>620</v>
       </c>
       <c r="R5" t="n">
-        <v>2204</v>
+        <v>1637</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1883516104</t>
+          <t>1979518055</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883516104</t>
+          <t>https://m.place.naver.com/place/1979518055</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
+          <t>보스턴짐 상갈점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy46@naver.com</t>
+          <t>bostongym44@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1398-7945</t>
+          <t>0507-1312-1996</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
+          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy46</t>
+          <t>https://www.instagram.com/bostongym_4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1017</v>
+        <v>1351</v>
       </c>
       <c r="Q6" t="n">
-        <v>620</v>
+        <v>756</v>
       </c>
       <c r="R6" t="n">
-        <v>1637</v>
+        <v>2107</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1979518055</t>
+          <t>1333671976</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979518055</t>
+          <t>https://m.place.naver.com/place/1333671976</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>보스턴짐 상갈점 헬스 PT</t>
+          <t>뷰티풀몬스터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bostongym44@naver.com</t>
+          <t>stryper1983@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-1996</t>
+          <t>0507-1412-1006</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
+          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bostongym_4</t>
+          <t>https://blog.naver.com/stryper1983</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="Q7" t="n">
-        <v>756</v>
+        <v>326</v>
       </c>
       <c r="R7" t="n">
-        <v>2107</v>
+        <v>1674</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1333671976</t>
+          <t>37489444</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333671976</t>
+          <t>https://m.place.naver.com/place/37489444</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>뷰티풀몬스터</t>
+          <t>헬스보이짐PT 상현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>stryper1983@naver.com</t>
+          <t>healthboy64@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-1006</t>
+          <t>0507-1383-8929</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
+          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/stryper1983</t>
+          <t>https://www.instagram.com/healthboy64/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1348</v>
+        <v>942</v>
       </c>
       <c r="Q8" t="n">
-        <v>326</v>
+        <v>716</v>
       </c>
       <c r="R8" t="n">
-        <v>1674</v>
+        <v>1658</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37489444</t>
+          <t>1266933778</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37489444</t>
+          <t>https://m.place.naver.com/place/1266933778</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐PT 상현점</t>
+          <t>넥스트짐 용인 강남대점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboy64@naver.com</t>
+          <t>nextgym04@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1383-8929</t>
+          <t>0507-1327-9679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
+          <t>경기도 용인시 기흥구 강남로 3 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy64/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>942</v>
+        <v>621</v>
       </c>
       <c r="Q9" t="n">
-        <v>716</v>
+        <v>116</v>
       </c>
       <c r="R9" t="n">
-        <v>1658</v>
+        <v>737</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1266933778</t>
+          <t>2078374448</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266933778</t>
+          <t>https://m.place.naver.com/place/2078374448</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>넥스트짐 용인 강남대점 헬스 PT</t>
+          <t>리플랜운동센터 재활.체형교정.PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nextgym04@naver.com</t>
+          <t>kyweee213@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1327-9679</t>
+          <t>0507-1304-3762</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 강남로 3 7층</t>
+          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/kyweee213</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>621</v>
+        <v>83</v>
       </c>
       <c r="Q10" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="R10" t="n">
-        <v>737</v>
+        <v>230</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2078374448</t>
+          <t>1269639617</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2078374448</t>
+          <t>https://m.place.naver.com/place/1269639617</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>청담피트니스</t>
+          <t>랩스휘트니스 신갈점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cdam2888@naver.com</t>
+          <t>rapsfit07@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1361-2889</t>
+          <t>0507-1306-2441</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 명지로60번길 8-12 4층</t>
+          <t>경기도 용인시 기흥구 신갈로 140 한솔플라자</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cdam2888</t>
+          <t>https://www.instagram.com/rapsfit07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1756</v>
+        <v>1150</v>
       </c>
       <c r="Q11" t="n">
-        <v>435</v>
+        <v>917</v>
       </c>
       <c r="R11" t="n">
-        <v>2191</v>
+        <v>2067</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1073785917</t>
+          <t>37302152</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073785917</t>
+          <t>https://m.place.naver.com/place/37302152</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1499,34 +1499,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>리플랜운동센터 재활.체형교정.PT</t>
+          <t>엔오엔짐 구성언남점 헬스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kyweee213@naver.com</t>
+          <t>non_gym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1304-3762</t>
+          <t>031-287-5559</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
+          <t>경기도 용인시 기흥구 석성로 257 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kyweee213</t>
+          <t>https://www.instagram.com/n.o.n_gym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>83</v>
+        <v>254</v>
       </c>
       <c r="Q12" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="R12" t="n">
-        <v>230</v>
+        <v>424</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1269639617</t>
+          <t>1417180452</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1269639617</t>
+          <t>https://m.place.naver.com/place/1417180452</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1598,34 +1598,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>랩스휘트니스 신갈점</t>
+          <t>상현 모션앤핏 재활PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rapsfit07@naver.com</t>
+          <t>motionandfit@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1306-2441</t>
+          <t>0507-1339-5312</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 신갈로 140 한솔플라자</t>
+          <t>경기도 용인시 수지구 광교마을로 83 4층 403호(상현동)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rapsfit07</t>
+          <t>http://pf.kakao.com/_gKxmmn/chat</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1646,7 +1646,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1150</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="n">
-        <v>917</v>
+        <v>56</v>
       </c>
       <c r="R13" t="n">
-        <v>2067</v>
+        <v>91</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,109 +1670,15 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>37302152</t>
+          <t>2055801698</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37302152</t>
+          <t>https://m.place.naver.com/place/2055801698</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>엔오엔짐 구성언남점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>non_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>031-287-5559</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 용인시 기흥구 석성로 257 1층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/n.o.n_gym</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>254</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>170</v>
-      </c>
-      <c r="R14" t="n">
-        <v>424</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1417180452</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1417180452</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엔오엔짐 구성언남점 헬스 PT</t>
+          <t>넥스트짐 처인구청점 헬스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>non_gym@naver.com</t>
+          <t>nextgym04@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>031-287-5559</t>
+          <t>0507-1397-9679</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 석성로 257 1층</t>
+          <t>경기도 용인시 처인구 금령로 86 9층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.o.n_gym</t>
+          <t>https://blog.naver.com/nextgym04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>254</v>
+        <v>3899</v>
       </c>
       <c r="Q12" t="n">
-        <v>170</v>
+        <v>1091</v>
       </c>
       <c r="R12" t="n">
-        <v>424</v>
+        <v>4990</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1417180452</t>
+          <t>1942211461</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1417180452</t>
+          <t>https://m.place.naver.com/place/1942211461</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>상현 모션앤핏 재활PT</t>
+          <t>피트인피티</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>motionandfit@naver.com</t>
+          <t>dailynfit@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1339-5312</t>
+          <t>0507-1416-0837</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교마을로 83 4층 403호(상현동)</t>
+          <t>경기도 용인시 기흥구 구갈로 55 지하1층 102호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gKxmmn/chat</t>
+          <t>https://www.dailynfit.com</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="Q13" t="n">
-        <v>56</v>
+        <v>256</v>
       </c>
       <c r="R13" t="n">
-        <v>91</v>
+        <v>516</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2055801698</t>
+          <t>1282849753</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055801698</t>
+          <t>https://m.place.naver.com/place/1282849753</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스타트짐</t>
+          <t>런던피트니스 &amp; 헬스 &amp; PT 보정점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>startgym9@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1411-8593</t>
+          <t>0507-1429-9680</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
+          <t>경기도 용인시 기흥구 죽전로 20 죽전누리에뜰 B동 B1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/start_gym_no.1</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>79</v>
+        <v>3589</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>570</v>
       </c>
       <c r="R3" t="n">
-        <v>113</v>
+        <v>4159</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1252102661</t>
+          <t>1409535054</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252102661</t>
+          <t>https://m.place.naver.com/place/1409535054</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,39 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비전휘트니스 수지점</t>
+          <t>스타트짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>visionfitness777@naver.com</t>
+          <t>startgym9@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1368-4687</t>
+          <t>0507-1411-8593</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
+          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/vision7</t>
+          <t>https://www.instagram.com/start_gym_no.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>841</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1363</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>2204</v>
+        <v>113</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1883516104</t>
+          <t>1252102661</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883516104</t>
+          <t>https://m.place.naver.com/place/1252102661</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
+          <t>비전휘트니스 수지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy46@naver.com</t>
+          <t>visionfitness777@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1398-7945</t>
+          <t>0507-1368-4687</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
+          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy46</t>
+          <t>https://litt.ly/vision7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1017</v>
+        <v>841</v>
       </c>
       <c r="Q5" t="n">
-        <v>620</v>
+        <v>1363</v>
       </c>
       <c r="R5" t="n">
-        <v>1637</v>
+        <v>2204</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1979518055</t>
+          <t>1883516104</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979518055</t>
+          <t>https://m.place.naver.com/place/1883516104</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>보스턴짐 상갈점 헬스 PT</t>
+          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bostongym44@naver.com</t>
+          <t>healthboy46@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1312-1996</t>
+          <t>0507-1398-7945</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
+          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bostongym_4</t>
+          <t>https://blog.naver.com/healthboy46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1351</v>
+        <v>1017</v>
       </c>
       <c r="Q6" t="n">
-        <v>756</v>
+        <v>620</v>
       </c>
       <c r="R6" t="n">
-        <v>2107</v>
+        <v>1637</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1333671976</t>
+          <t>1979518055</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333671976</t>
+          <t>https://m.place.naver.com/place/1979518055</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뷰티풀몬스터</t>
+          <t>보스턴짐 상갈점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>stryper1983@naver.com</t>
+          <t>bostongym44@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1412-1006</t>
+          <t>0507-1312-1996</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
+          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/stryper1983</t>
+          <t>https://www.instagram.com/bostongym_4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="Q7" t="n">
-        <v>326</v>
+        <v>756</v>
       </c>
       <c r="R7" t="n">
-        <v>1674</v>
+        <v>2107</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37489444</t>
+          <t>1333671976</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37489444</t>
+          <t>https://m.place.naver.com/place/1333671976</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐PT 상현점</t>
+          <t>뷰티풀몬스터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy64@naver.com</t>
+          <t>stryper1983@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1383-8929</t>
+          <t>0507-1412-1006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
+          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy64/</t>
+          <t>https://blog.naver.com/stryper1983</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>942</v>
+        <v>1348</v>
       </c>
       <c r="Q8" t="n">
-        <v>716</v>
+        <v>326</v>
       </c>
       <c r="R8" t="n">
-        <v>1658</v>
+        <v>1674</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1266933778</t>
+          <t>37489444</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266933778</t>
+          <t>https://m.place.naver.com/place/37489444</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>넥스트짐 용인 강남대점 헬스 PT</t>
+          <t>헬스보이짐PT 상현점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nextgym04@naver.com</t>
+          <t>healthboy64@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1327-9679</t>
+          <t>0507-1383-8929</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 강남로 3 7층</t>
+          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/healthboy64/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>621</v>
+        <v>942</v>
       </c>
       <c r="Q9" t="n">
-        <v>116</v>
+        <v>716</v>
       </c>
       <c r="R9" t="n">
-        <v>737</v>
+        <v>1658</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2078374448</t>
+          <t>1266933778</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2078374448</t>
+          <t>https://m.place.naver.com/place/1266933778</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리플랜운동센터 재활.체형교정.PT</t>
+          <t>넥스트짐 용인 강남대점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kyweee213@naver.com</t>
+          <t>nextgym04@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-3762</t>
+          <t>0507-1327-9679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
+          <t>경기도 용인시 기흥구 강남로 3 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kyweee213</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>83</v>
+        <v>621</v>
       </c>
       <c r="Q10" t="n">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="R10" t="n">
-        <v>230</v>
+        <v>738</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1269639617</t>
+          <t>2078374448</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1269639617</t>
+          <t>https://m.place.naver.com/place/2078374448</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>랩스휘트니스 신갈점</t>
+          <t>리플랜운동센터 재활.체형교정.PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rapsfit07@naver.com</t>
+          <t>kyweee213@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1306-2441</t>
+          <t>0507-1304-3762</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 신갈로 140 한솔플라자</t>
+          <t>경기도 용인시 기흥구 새천년로16번길 7 2층 201호(신갈동)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rapsfit07</t>
+          <t>https://blog.naver.com/kyweee213</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1150</v>
+        <v>83</v>
       </c>
       <c r="Q11" t="n">
-        <v>917</v>
+        <v>147</v>
       </c>
       <c r="R11" t="n">
-        <v>2067</v>
+        <v>230</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37302152</t>
+          <t>1269639617</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37302152</t>
+          <t>https://m.place.naver.com/place/1269639617</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1499,34 +1499,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>넥스트짐 처인구청점 헬스 PT</t>
+          <t>랩스휘트니스 신갈점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nextgym04@naver.com</t>
+          <t>rapsfit07@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1397-9679</t>
+          <t>0507-1306-2441</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 금령로 86 9층</t>
+          <t>경기도 용인시 기흥구 신갈로 140 한솔플라자</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nextgym04</t>
+          <t>https://www.instagram.com/rapsfit07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3899</v>
+        <v>1150</v>
       </c>
       <c r="Q12" t="n">
-        <v>1091</v>
+        <v>917</v>
       </c>
       <c r="R12" t="n">
-        <v>4990</v>
+        <v>2067</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,109 +1576,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1942211461</t>
+          <t>37302152</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942211461</t>
+          <t>https://m.place.naver.com/place/37302152</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>피트인피티</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dailynfit@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1416-0837</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 용인시 기흥구 구갈로 55 지하1층 102호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.dailynfit.com</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>260</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>256</v>
-      </c>
-      <c r="R13" t="n">
-        <v>516</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1282849753</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1282849753</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -718,10 +718,10 @@
         <v>3589</v>
       </c>
       <c r="Q3" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="R3" t="n">
-        <v>4159</v>
+        <v>4160</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="Q5" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="R5" t="n">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="Q6" t="n">
         <v>620</v>
       </c>
       <c r="R6" t="n">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="Q7" t="n">
         <v>756</v>
       </c>
       <c r="R7" t="n">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>런던피트니스 &amp; 헬스 &amp; PT 보정점</t>
+          <t>스타트짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>startgym9@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1429-9680</t>
+          <t>0507-1411-8593</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 죽전로 20 죽전누리에뜰 B동 B1층</t>
+          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>https://www.instagram.com/start_gym_no.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3589</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="n">
-        <v>571</v>
+        <v>34</v>
       </c>
       <c r="R3" t="n">
-        <v>4160</v>
+        <v>113</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,56 +730,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1409535054</t>
+          <t>1252102661</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409535054</t>
+          <t>https://m.place.naver.com/place/1252102661</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스타트짐</t>
+          <t>비전휘트니스 수지점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>startgym9@naver.com</t>
+          <t>visionfitness777@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1411-8593</t>
+          <t>0507-1368-4687</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
+          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/start_gym_no.1</t>
+          <t>https://litt.ly/vision7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>79</v>
+        <v>842</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>1364</v>
       </c>
       <c r="R4" t="n">
-        <v>113</v>
+        <v>2206</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1252102661</t>
+          <t>1883516104</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252102661</t>
+          <t>https://m.place.naver.com/place/1883516104</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비전휘트니스 수지점</t>
+          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>visionfitness777@naver.com</t>
+          <t>healthboy46@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-4687</t>
+          <t>0507-1398-7945</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
+          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/vision7</t>
+          <t>https://blog.naver.com/healthboy46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>842</v>
+        <v>1014</v>
       </c>
       <c r="Q5" t="n">
-        <v>1364</v>
+        <v>620</v>
       </c>
       <c r="R5" t="n">
-        <v>2206</v>
+        <v>1634</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1883516104</t>
+          <t>1979518055</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883516104</t>
+          <t>https://m.place.naver.com/place/1979518055</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
+          <t>보스턴짐 상갈점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy46@naver.com</t>
+          <t>bostongym44@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1398-7945</t>
+          <t>0507-1312-1996</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
+          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy46</t>
+          <t>https://www.instagram.com/bostongym_4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1014</v>
+        <v>1352</v>
       </c>
       <c r="Q6" t="n">
-        <v>620</v>
+        <v>756</v>
       </c>
       <c r="R6" t="n">
-        <v>1634</v>
+        <v>2108</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1979518055</t>
+          <t>1333671976</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979518055</t>
+          <t>https://m.place.naver.com/place/1333671976</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>보스턴짐 상갈점 헬스 PT</t>
+          <t>뷰티풀몬스터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bostongym44@naver.com</t>
+          <t>stryper1983@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-1996</t>
+          <t>0507-1412-1006</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
+          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bostongym_4</t>
+          <t>https://blog.naver.com/stryper1983</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="Q7" t="n">
-        <v>756</v>
+        <v>326</v>
       </c>
       <c r="R7" t="n">
-        <v>2108</v>
+        <v>1674</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1333671976</t>
+          <t>37489444</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333671976</t>
+          <t>https://m.place.naver.com/place/37489444</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>뷰티풀몬스터</t>
+          <t>헬스보이짐PT 상현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>stryper1983@naver.com</t>
+          <t>healthboy64@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-1006</t>
+          <t>0507-1383-8929</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
+          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/stryper1983</t>
+          <t>https://www.instagram.com/healthboy64/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1348</v>
+        <v>943</v>
       </c>
       <c r="Q8" t="n">
-        <v>326</v>
+        <v>717</v>
       </c>
       <c r="R8" t="n">
-        <v>1674</v>
+        <v>1660</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1200,47 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37489444</t>
+          <t>1266933778</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37489444</t>
+          <t>https://m.place.naver.com/place/1266933778</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐PT 상현점</t>
+          <t>넥스트짐 용인기흥구청점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboy64@naver.com</t>
+          <t>nextgym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1383-8929</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
+          <t>경기도 용인시 기흥구 구갈로 70 구갈메가타운 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy64/</t>
+          <t>https://www.instagram.com/nextgym_01_official</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>942</v>
+        <v>3698</v>
       </c>
       <c r="Q9" t="n">
-        <v>716</v>
+        <v>1486</v>
       </c>
       <c r="R9" t="n">
-        <v>1658</v>
+        <v>5184</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1266933778</t>
+          <t>21710456</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266933778</t>
+          <t>https://m.place.naver.com/place/21710456</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="Q10" t="n">
         <v>117</v>
       </c>
       <c r="R10" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1398,7 +1394,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1492,101 +1488,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>랩스휘트니스 신갈점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>rapsfit07@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1306-2441</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 용인시 기흥구 신갈로 140 한솔플라자</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/rapsfit07</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1150</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>917</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2067</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>37302152</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37302152</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용인_PT.xlsx
+++ b/naver-place-crawler/results_health/용인_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dbtndnjs6503</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zfgx</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스타트짐</t>
+          <t>런던피트니스 &amp; 헬스 &amp; PT 보정점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>startgym9@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1411-8593</t>
+          <t>0507-1429-9680</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
+          <t>경기도 용인시 기흥구 죽전로 20 죽전누리에뜰 B동 B1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/start_gym_no.1</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>79</v>
+        <v>3594</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>113</v>
+        <v>4166</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1252102661</t>
+          <t>1409535054</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252102661</t>
+          <t>https://m.place.naver.com/place/1409535054</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,39 +751,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비전휘트니스 수지점</t>
+          <t>스타트짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>visionfitness777@naver.com</t>
+          <t>startgym9@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1368-4687</t>
+          <t>0507-1411-8593</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
+          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 2층 (스타트짐)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/vision7</t>
+          <t>https://www.instagram.com/start_gym_no.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>842</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1364</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>2206</v>
+        <v>113</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1883516104</t>
+          <t>1252102661</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883516104</t>
+          <t>https://m.place.naver.com/place/1252102661</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
+          <t>비전휘트니스 수지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy46@naver.com</t>
+          <t>visionfitness77@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1398-7945</t>
+          <t>0507-1368-4687</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
+          <t>경기도 용인시 수지구 성복2로76번길 26-4 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy46</t>
+          <t>https://litt.ly/vision7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,15 +887,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4snut</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1014</v>
+        <v>842</v>
       </c>
       <c r="Q5" t="n">
-        <v>620</v>
+        <v>1366</v>
       </c>
       <c r="R5" t="n">
-        <v>1634</v>
+        <v>2208</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1979518055</t>
+          <t>1883516104</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979518055</t>
+          <t>https://m.place.naver.com/place/1883516104</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>보스턴짐 상갈점 헬스 PT</t>
+          <t>헬스보이짐PT&amp;필라걸&amp;골프인 수지점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bostongym44@naver.com</t>
+          <t>healthboy46@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1312-1996</t>
+          <t>0507-1398-7945</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
+          <t>경기도 용인시 수지구 신봉2로 2 지하1층, 지하2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bostongym_4</t>
+          <t>https://blog.naver.com/healthboy46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +985,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +996,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1352</v>
+        <v>1014</v>
       </c>
       <c r="Q6" t="n">
-        <v>756</v>
+        <v>620</v>
       </c>
       <c r="R6" t="n">
-        <v>2108</v>
+        <v>1634</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1020,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1333671976</t>
+          <t>1979518055</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333671976</t>
+          <t>https://m.place.naver.com/place/1979518055</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뷰티풀몬스터</t>
+          <t>보스턴짐 상갈점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>stryper1983@naver.com</t>
+          <t>bostongym44@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1412-1006</t>
+          <t>0507-1312-1996</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
+          <t>경기도 용인시 기흥구 금화로 103 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/stryper1983</t>
+          <t>https://www.instagram.com/bostongym_4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1090,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1348</v>
+        <v>1355</v>
       </c>
       <c r="Q7" t="n">
-        <v>326</v>
+        <v>756</v>
       </c>
       <c r="R7" t="n">
-        <v>1674</v>
+        <v>2111</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1114,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37489444</t>
+          <t>1333671976</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37489444</t>
+          <t>https://m.place.naver.com/place/1333671976</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1136,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐PT 상현점</t>
+          <t>뷰티풀몬스터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy64@naver.com</t>
+          <t>stryper1983@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1383-8929</t>
+          <t>0507-1412-1006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
+          <t>경기도 용인시 처인구 금령로71번길 16 대흥빌딩 2층, 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy64/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1168,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1170,10 +1178,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wj3k</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>943</v>
+        <v>1348</v>
       </c>
       <c r="Q8" t="n">
-        <v>717</v>
+        <v>326</v>
       </c>
       <c r="R8" t="n">
-        <v>1660</v>
+        <v>1674</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1212,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1266933778</t>
+          <t>37489444</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266933778</t>
+          <t>https://m.place.naver.com/place/37489444</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,30 +1229,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>넥스트짐 용인기흥구청점 헬스 PT</t>
+          <t>헬스보이짐PT 상현점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nextgym1@naver.com</t>
+          <t>healthboy64@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1383-8929</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 구갈로 70 구갈메가타운 10층</t>
+          <t>경기도 용인시 수지구 광교중앙로296번길 10 지하1층 비101,비102, 비103호(상현동, 광교 리치안 오피스텔)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nextgym_01_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1266,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1260,10 +1276,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46jr5</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3698</v>
+        <v>943</v>
       </c>
       <c r="Q9" t="n">
-        <v>1486</v>
+        <v>718</v>
       </c>
       <c r="R9" t="n">
-        <v>5184</v>
+        <v>1661</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1310,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>21710456</t>
+          <t>1266933778</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21710456</t>
+          <t>https://m.place.naver.com/place/1266933778</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1428,7 +1448,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kyweee213</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,20 +1458,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44aui</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1487,6 +1511,300 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>랩스휘트니스 신갈점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rapsfit07@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1306-2441</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 신갈로 140 한솔플라자</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gymi</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>917</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>37302152</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37302152</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>넥스트짐 처인구청점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nextgym04@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1397-9679</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 금령로 86 9층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4czes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>3906</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1094</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1942211461</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1942211461</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>피트인피티</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>gpta4@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1416-0837</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 구갈로 55 지하1층 102호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.dailynfit.com</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4s0cxy</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>258</v>
+      </c>
+      <c r="R14" t="n">
+        <v>518</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1282849753</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282849753</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
